--- a/new-whoop-model .xlsx
+++ b/new-whoop-model .xlsx
@@ -24467,36 +24467,28 @@
         <v>540</v>
       </c>
       <c r="D12" s="46">
-        <f>Assumptions!$F$74</f>
-        <v>0.115874493309381</v>
+        <f>Assumptions!$F$73</f>
       </c>
       <c r="E12" s="46">
-        <f>Assumptions!$F$74</f>
-        <v>0.115874493309381</v>
+        <f>Assumptions!$F$73</f>
       </c>
       <c r="F12" s="46">
-        <f>Assumptions!$F$74</f>
-        <v>0.115874493309381</v>
+        <f>Assumptions!$F$73</f>
       </c>
       <c r="G12" s="46">
-        <f>Assumptions!$F$74</f>
-        <v>0.115874493309381</v>
+        <f>Assumptions!$F$73</f>
       </c>
       <c r="H12" s="46">
-        <f>Assumptions!$F$74</f>
-        <v>0.115874493309381</v>
+        <f>Assumptions!$F$73</f>
       </c>
       <c r="I12" s="46">
-        <f>Assumptions!$F$74</f>
-        <v>0.115874493309381</v>
+        <f>Assumptions!$F$73</f>
       </c>
       <c r="J12" s="46">
-        <f>Assumptions!$F$74</f>
-        <v>0.115874493309381</v>
+        <f>Assumptions!$F$73</f>
       </c>
       <c r="K12" s="46">
-        <f>Assumptions!$F$74</f>
-        <v>0.115874493309381</v>
+        <f>Assumptions!$F$73</f>
       </c>
       <c r="L12" s="406"/>
       <c r="M12" s="406" t="s">
@@ -25436,20 +25428,19 @@
         <v>1722</v>
       </c>
       <c r="B60" s="1288">
-        <v>2055.85</v>
+        <v>2098.7611</v>
       </c>
       <c r="C60" s="1288">
-        <v>2504.21</v>
+        <v>2546.6192</v>
       </c>
       <c r="D60" s="1288">
-        <v>2657.5</v>
+        <v>2699.907</v>
       </c>
       <c r="E60" s="1105">
-        <v>153.29</v>
+        <v>153.2879</v>
       </c>
       <c r="F60" s="1106">
-        <f>D60/$C$52-1</f>
-        <v>-0.73688118811881187</v>
+        <v>-0.732682</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
@@ -25457,20 +25448,19 @@
         <v>51</v>
       </c>
       <c r="B61" s="1288">
-        <v>6616.64</v>
+        <v>7108.0254</v>
       </c>
       <c r="C61" s="1288">
-        <v>7336.16</v>
+        <v>7826.643</v>
       </c>
       <c r="D61" s="1288">
-        <v>8276.25</v>
+        <v>8766.7298</v>
       </c>
       <c r="E61" s="1105">
-        <v>940.09</v>
+        <v>940.0868</v>
       </c>
       <c r="F61" s="1106">
-        <f>D61/$C$52-1</f>
-        <v>-0.18056930693069306</v>
+        <v>-0.132007</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
@@ -25478,20 +25468,19 @@
         <v>55</v>
       </c>
       <c r="B62" s="1288">
-        <v>18877.82</v>
+        <v>27405.5758</v>
       </c>
       <c r="C62" s="1288">
-        <v>19882</v>
+        <v>28427.7183</v>
       </c>
       <c r="D62" s="1288">
-        <v>22596.33</v>
+        <v>31375.6246</v>
       </c>
       <c r="E62" s="1105">
-        <v>2714.32</v>
+        <v>2947.9063</v>
       </c>
       <c r="F62" s="1106">
-        <f>D62/$C$52-1</f>
-        <v>1.2372603960396042</v>
+        <v>2.106497</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.2">
@@ -25499,20 +25488,19 @@
         <v>1723</v>
       </c>
       <c r="B63" s="1289">
-        <v>7362.36</v>
+        <v>8070.9242</v>
       </c>
       <c r="C63" s="1289">
-        <v>8090.59</v>
+        <v>8797.9604</v>
       </c>
       <c r="D63" s="1289">
-        <v>9030.68</v>
+        <v>9742.683</v>
       </c>
       <c r="E63" s="1107">
-        <v>940.09</v>
+        <v>944.7226</v>
       </c>
       <c r="F63" s="1108">
-        <f>D63/$C$52-1</f>
-        <v>-0.10587326732673263</v>
+        <v>-0.035378</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -29591,7 +29579,7 @@
         <v>50.175609756097558</v>
       </c>
       <c r="I6" s="291">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J6" s="316">
         <f>D6*I6</f>
@@ -29706,10 +29694,15 @@
         <f>(E9*1000 - Assumptions!$F$61 + Assumptions!$F$62)/Assumptions!$F$54</f>
         <v>30.04805731707317</v>
       </c>
-      <c r="I9" s="312"/>
+      <c r="I9" s="312">
+        <v>0.4</v>
+      </c>
       <c r="J9" s="309"/>
       <c r="K9" s="320" t="s">
         <v>2023</v>
+      </c>
+      <c r="J9">
+        <f>D9*I9</f>
       </c>
     </row>
     <row r="10" spans="1:11" ht="27" x14ac:dyDescent="0.2">
@@ -29891,8 +29884,7 @@
       <c r="G16" s="327"/>
       <c r="H16" s="327"/>
       <c r="I16" s="328">
-        <f>I6+I10+I13+I14</f>
-        <v>1</v>
+        <f>I6+I9+I10+I13+I14</f>
       </c>
       <c r="J16" s="329"/>
       <c r="K16" s="330"/>
@@ -29907,8 +29899,7 @@
       <c r="B18" s="331"/>
       <c r="C18" s="331"/>
       <c r="D18" s="341">
-        <f>J6+J10+J13+J14</f>
-        <v>7.1068843749999999</v>
+        <f>J9+J10+J13+J14</f>
       </c>
       <c r="E18" s="331"/>
       <c r="F18" s="331"/>
@@ -33056,9 +33047,8 @@
       <c r="A14" s="118" t="s">
         <v>1357</v>
       </c>
-      <c r="B14" s="134" t="e">
-        <f>ARPU!#REF!</f>
-        <v>#REF!</v>
+      <c r="B14" s="134">
+        <f>IF(ABS(ARPU!D8-ARPU!D20)/ARPU!D20&lt;0.1,"✓","⚠")</f>
       </c>
       <c r="C14" s="134" t="s">
         <v>1358</v>
@@ -36604,8 +36594,10 @@
       <c r="A3" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="581" t="s">
-        <v>51</v>
+      <c r="B3" s="581" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
       </c>
       <c r="C3" s="1133" t="s">
         <v>1750</v>
@@ -38596,8 +38588,7 @@
         <v>9.7549999999999984E-2</v>
       </c>
       <c r="F73" s="602">
-        <f>IF($B$3="Bear",C73,IF($B$3="Bull",E73,D73))</f>
-        <v>0.10844999999999999</v>
+        <f>IF($B$3="Bear",C73,IF($B$3="Bull",E73,IF($B$3="ProbWeighted",J73,D73)))</f>
       </c>
       <c r="G73" s="584" t="s">
         <v>73</v>
@@ -38607,6 +38598,9 @@
       </c>
       <c r="I73" s="894"/>
       <c r="J73" s="415"/>
+      <c r="J73">
+        <f>$C$2*C73+$E$2*D73+$G$2*E73</f>
+      </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="27"/>
@@ -40890,15 +40884,13 @@
         <v>0.13</v>
       </c>
       <c r="F172" s="820">
-        <f>IF($B$3="Bear",C172,IF($B$3="Bull",E173,IF($B$3="ProbWeighted",J172,D172)))</f>
-        <v>0.108</v>
+        <f>IF($B$3="Bear",C172,IF($B$3="Bull",E172,IF($B$3="ProbWeighted",J172,D172)))</f>
       </c>
       <c r="G172" s="821" t="s">
         <v>87</v>
       </c>
       <c r="J172" s="1021">
-        <f>$C$2*C172+$E$2*D172+$G$2*E173</f>
-        <v>9.7000000000000003E-2</v>
+        <f>$C$2*C172+$E$2*D172+$G$2*E172</f>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.2">
@@ -40918,15 +40910,13 @@
         <v>0.09</v>
       </c>
       <c r="F173" s="820">
-        <f>IF($B$3="Bear",C173,IF($B$3="Bull",E174,IF($B$3="ProbWeighted",J173,D173)))</f>
-        <v>7.8E-2</v>
+        <f>IF($B$3="Bear",C173,IF($B$3="Bull",E173,IF($B$3="ProbWeighted",J173,D173)))</f>
       </c>
       <c r="G173" s="821" t="s">
         <v>87</v>
       </c>
       <c r="J173" s="1021">
-        <f>$C$2*C173+$E$2*D173+$G$2*E174</f>
-        <v>7.2000000000000008E-2</v>
+        <f>$C$2*C173+$E$2*D173+$G$2*E173</f>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.2">
@@ -40946,15 +40936,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F174" s="820">
-        <f>IF($B$3="Bear",C174,IF($B$3="Bull",#REF!,IF($B$3="ProbWeighted",J174,D174)))</f>
-        <v>5.8999999999999997E-2</v>
+        <f>IF($B$3="Bear",C174,IF($B$3="Bull",E174,IF($B$3="ProbWeighted",J174,D174)))</f>
       </c>
       <c r="G174" s="821" t="s">
         <v>87</v>
       </c>
-      <c r="J174" s="1021" t="e">
-        <f>$C$2*C174+$E$2*D174+$G$2*#REF!</f>
-        <v>#REF!</v>
+      <c r="J174" s="1021">
+        <f>$C$2*C174+$E$2*D174+$G$2*E174</f>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.2">
@@ -40973,8 +40961,7 @@
         <v>10.924108107214609</v>
       </c>
       <c r="E176" s="824">
-        <f>2.5*(1+E167)*(1+E168)*(1+E169)*(1+E170)*(1+E171)*(1+E173)*(1+E174)*(1+E172)</f>
-        <v>18.106692079161522</v>
+        <f>2.5*(1+E167)*(1+E168)*(1+E169)*(1+E170)*(1+E171)*(1+E172)*(1+E173)*(1+E174)</f>
       </c>
       <c r="F176" s="825">
         <f>2.5*(1+F167)*(1+F168)*(1+F169)*(1+F170)*(1+F171)*(1+F172)*(1+F173)*(1+F174)</f>
@@ -42087,12 +42074,10 @@
         <v>0.108</v>
       </c>
       <c r="E233" s="1269">
-        <f>E173</f>
-        <v>0.09</v>
+        <f>E172</f>
       </c>
       <c r="F233" s="1265">
-        <f>$C$2*C172+$E$2*D172+$G$2*E173</f>
-        <v>9.7000000000000003E-2</v>
+        <f>$C$2*C172+$E$2*D172+$G$2*E172</f>
       </c>
       <c r="G233" s="1268">
         <f>$C$2*C172</f>
@@ -42103,16 +42088,14 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="I233" s="1270">
-        <f>$G$2*E173</f>
-        <v>2.7E-2</v>
+        <f>$G$2*E172</f>
       </c>
       <c r="J233" s="1267">
         <f>F172</f>
         <v>0.108</v>
       </c>
       <c r="K233" s="1268">
-        <f>E173-C172</f>
-        <v>9.999999999999995E-3</v>
+        <f>E172-C172</f>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.2">
@@ -42131,12 +42114,10 @@
         <v>7.8E-2</v>
       </c>
       <c r="E234" s="1275">
-        <f>E174</f>
-        <v>7.0000000000000007E-2</v>
+        <f>E173</f>
       </c>
       <c r="F234" s="1272">
-        <f>$C$2*C173+$E$2*D173+$G$2*E174</f>
-        <v>7.2000000000000008E-2</v>
+        <f>$C$2*C173+$E$2*D173+$G$2*E173</f>
       </c>
       <c r="G234" s="1275">
         <f>$C$2*C173</f>
@@ -42147,16 +42128,14 @@
         <v>3.9E-2</v>
       </c>
       <c r="I234" s="1276">
-        <f>$G$2*E174</f>
-        <v>2.1000000000000001E-2</v>
+        <f>$G$2*E173</f>
       </c>
       <c r="J234" s="1274">
         <f>F173</f>
         <v>7.8E-2</v>
       </c>
       <c r="K234" s="1275">
-        <f>E174-C173</f>
-        <v>1.0000000000000009E-2</v>
+        <f>E173-C173</f>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.2">
@@ -42174,13 +42153,11 @@
         <f>D174</f>
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="E235" s="1269" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F235" s="1265" t="e">
-        <f>$C$2*C174+$E$2*D174+$G$2*#REF!</f>
-        <v>#REF!</v>
+      <c r="E235" s="1269">
+        <f>E174</f>
+      </c>
+      <c r="F235" s="1265">
+        <f>$C$2*C174+$E$2*D174+$G$2*E174</f>
       </c>
       <c r="G235" s="1269">
         <f>$C$2*C174</f>
@@ -42190,17 +42167,15 @@
         <f>$E$2*D174</f>
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="I235" s="1270" t="e">
-        <f>$G$2*#REF!</f>
-        <v>#REF!</v>
+      <c r="I235" s="1270">
+        <f>$G$2*E174</f>
       </c>
       <c r="J235" s="1292">
         <f>F174</f>
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="K235" s="1269" t="e">
-        <f>#REF!-C174</f>
-        <v>#REF!</v>
+      <c r="K235" s="1269">
+        <f>E174-C174</f>
       </c>
     </row>
     <row r="236" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -48705,7 +48680,7 @@
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="489">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19" s="493"/>
       <c r="F19" s="493"/>

--- a/new-whoop-model .xlsx
+++ b/new-whoop-model .xlsx
@@ -24467,28 +24467,28 @@
         <v>540</v>
       </c>
       <c r="D12" s="46">
-        <f>Assumptions!$F$73</f>
+        <f>Assumptions!$F$74</f>
       </c>
       <c r="E12" s="46">
-        <f>Assumptions!$F$73</f>
+        <f>Assumptions!$F$74</f>
       </c>
       <c r="F12" s="46">
-        <f>Assumptions!$F$73</f>
+        <f>Assumptions!$F$74</f>
       </c>
       <c r="G12" s="46">
-        <f>Assumptions!$F$73</f>
+        <f>Assumptions!$F$74</f>
       </c>
       <c r="H12" s="46">
-        <f>Assumptions!$F$73</f>
+        <f>Assumptions!$F$74</f>
       </c>
       <c r="I12" s="46">
-        <f>Assumptions!$F$73</f>
+        <f>Assumptions!$F$74</f>
       </c>
       <c r="J12" s="46">
-        <f>Assumptions!$F$73</f>
+        <f>Assumptions!$F$74</f>
       </c>
       <c r="K12" s="46">
-        <f>Assumptions!$F$73</f>
+        <f>Assumptions!$F$74</f>
       </c>
       <c r="L12" s="406"/>
       <c r="M12" s="406" t="s">
@@ -25428,19 +25428,19 @@
         <v>1722</v>
       </c>
       <c r="B60" s="1288">
-        <v>2098.7611</v>
+        <v>2048.8935</v>
       </c>
       <c r="C60" s="1288">
-        <v>2546.6192</v>
+        <v>2496.7516</v>
       </c>
       <c r="D60" s="1288">
-        <v>2699.907</v>
+        <v>2650.0394</v>
       </c>
       <c r="E60" s="1105">
         <v>153.2879</v>
       </c>
       <c r="F60" s="1106">
-        <v>-0.732682</v>
+        <v>-0.73762</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
@@ -25448,19 +25448,19 @@
         <v>51</v>
       </c>
       <c r="B61" s="1288">
-        <v>7108.0254</v>
+        <v>6601.9352</v>
       </c>
       <c r="C61" s="1288">
-        <v>7826.643</v>
+        <v>7320.5528</v>
       </c>
       <c r="D61" s="1288">
-        <v>8766.7298</v>
+        <v>8260.6396</v>
       </c>
       <c r="E61" s="1105">
         <v>940.0868</v>
       </c>
       <c r="F61" s="1106">
-        <v>-0.132007</v>
+        <v>-0.182115</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
@@ -25468,19 +25468,19 @@
         <v>55</v>
       </c>
       <c r="B62" s="1288">
-        <v>27405.5758</v>
+        <v>23635.5291</v>
       </c>
       <c r="C62" s="1288">
-        <v>28427.7183</v>
+        <v>24657.6716</v>
       </c>
       <c r="D62" s="1288">
-        <v>31375.6246</v>
+        <v>27605.5779</v>
       </c>
       <c r="E62" s="1105">
         <v>2947.9063</v>
       </c>
       <c r="F62" s="1106">
-        <v>2.106497</v>
+        <v>1.733226</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.2">
@@ -25488,19 +25488,19 @@
         <v>1723</v>
       </c>
       <c r="B63" s="1289">
-        <v>8070.9242</v>
+        <v>7458.6336</v>
       </c>
       <c r="C63" s="1289">
-        <v>8797.9604</v>
+        <v>8185.6698</v>
       </c>
       <c r="D63" s="1289">
-        <v>9742.683</v>
+        <v>9130.3924</v>
       </c>
       <c r="E63" s="1107">
         <v>944.7226</v>
       </c>
       <c r="F63" s="1108">
-        <v>-0.035378</v>
+        <v>-0.096001</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
